--- a/tools/import.xlsx
+++ b/tools/import.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZAS-TRAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD4FF33-8DFE-41F0-94D6-2DFA64CE21AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8E4D9A-8405-401C-AC10-755E2264B44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{33A15B55-7243-45E8-A84E-40C4CE8561A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="Equipment" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
